--- a/results/ads_intensive_stages/estimates/ads_intensive_stages_both_estimates.xlsx
+++ b/results/ads_intensive_stages/estimates/ads_intensive_stages_both_estimates.xlsx
@@ -410,7 +410,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Total Shares</t>
+          <t>log(Total shares)</t>
         </is>
       </c>
     </row>
@@ -438,7 +438,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Total Reactions</t>
+          <t>log(Total reactions)</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Total Comments</t>
+          <t>log(Total comments)</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Verifiable Posts + Shares</t>
+          <t>log(Verifiable posts + shares)</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Non Verifiable Posts + Shares</t>
+          <t>log(Non-verifiable posts + shares)</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>True Posts + Shares</t>
+          <t>log(True posts + shares)</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fake Posts + Shares</t>
+          <t>log(Fake posts + shares)</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Number of Posts + Shares (English)</t>
+          <t>log(Number of posts + shares, English)</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Positive COVID Posts + Shares</t>
+          <t>log(Positive COVID posts + shares)</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Neutral COVID Posts + Shares</t>
+          <t>log(Neutral COVID posts + shares)</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Negative COVID Posts + Shares</t>
+          <t>log(Negative COVID posts + shares)</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>COVID Posts + Shares</t>
+          <t>log(COVID posts + shares)</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Positive Vaccine Posts + Shares</t>
+          <t>log(Positive vaccine posts + shares)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Neutral Vaccine Posts + Shares</t>
+          <t>log(Neutral vaccine posts + shares)</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Negative Vaccine Posts + Shares</t>
+          <t>log(Negative vaccine posts + shares)</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaccine Posts + Shares</t>
+          <t>log(Vaccine posts + shares)</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Total Shares</t>
+          <t>log(Total shares)</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Total Reactions</t>
+          <t>log(Total reactions)</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Total Comments</t>
+          <t>log(Total comments)</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Verifiable Posts + Shares</t>
+          <t>log(Verifiable posts + shares)</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Non Verifiable Posts + Shares</t>
+          <t>log(Non-verifiable posts + shares)</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>True Posts + Shares</t>
+          <t>log(True posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fake Posts + Shares</t>
+          <t>log(Fake posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Number of Posts + Shares (English)</t>
+          <t>log(Number of posts + shares, English)</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Positive COVID Posts + Shares</t>
+          <t>log(Positive COVID posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Neutral COVID Posts + Shares</t>
+          <t>log(Neutral COVID posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Negative COVID Posts + Shares</t>
+          <t>log(Negative COVID posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>COVID Posts + Shares</t>
+          <t>log(COVID posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Positive Vaccine Posts + Shares</t>
+          <t>log(Positive vaccine posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Neutral Vaccine Posts + Shares</t>
+          <t>log(Neutral vaccine posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Negative Vaccine Posts + Shares</t>
+          <t>log(Negative vaccine posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vaccine Posts + Shares</t>
+          <t>log(Vaccine posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Total Shares</t>
+          <t>log(Total shares)</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Total Reactions</t>
+          <t>log(Total reactions)</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Total Comments</t>
+          <t>log(Total comments)</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Verifiable Posts + Shares</t>
+          <t>log(Verifiable posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Non Verifiable Posts + Shares</t>
+          <t>log(Non-verifiable posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>True Posts + Shares</t>
+          <t>log(True posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fake Posts + Shares</t>
+          <t>log(Fake posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Number of Posts + Shares (English)</t>
+          <t>log(Number of posts + shares, English)</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Positive COVID Posts + Shares</t>
+          <t>log(Positive COVID posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Neutral COVID Posts + Shares</t>
+          <t>log(Neutral COVID posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Negative COVID Posts + Shares</t>
+          <t>log(Negative COVID posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>COVID Posts + Shares</t>
+          <t>log(COVID posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Positive Vaccine Posts + Shares</t>
+          <t>log(Positive vaccine posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Neutral Vaccine Posts + Shares</t>
+          <t>log(Neutral vaccine posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Negative Vaccine Posts + Shares</t>
+          <t>log(Negative vaccine posts + shares)</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vaccine Posts + Shares</t>
+          <t>log(Vaccine posts + shares)</t>
         </is>
       </c>
     </row>
